--- a/data/Other Recommended Order.xlsx
+++ b/data/Other Recommended Order.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Transfer Plan" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Other Recommended Order.xlsx
+++ b/data/Other Recommended Order.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Transfer Plan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Other Recommended Order.xlsx
+++ b/data/Other Recommended Order.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N254"/>
+  <dimension ref="A1:O254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,6 +489,11 @@
           <t>Deal Terms</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Buy Month</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,6 +539,7 @@
         <v>48</v>
       </c>
       <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -579,6 +585,7 @@
         <v>47</v>
       </c>
       <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -624,6 +631,7 @@
         <v>51</v>
       </c>
       <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -669,6 +677,7 @@
         <v>62</v>
       </c>
       <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -714,6 +723,7 @@
         <v>29</v>
       </c>
       <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -759,6 +769,7 @@
         <v>29</v>
       </c>
       <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -804,6 +815,7 @@
         <v>32</v>
       </c>
       <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -849,6 +861,7 @@
         <v>47</v>
       </c>
       <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -894,6 +907,7 @@
         <v>57</v>
       </c>
       <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -939,6 +953,7 @@
         <v>30</v>
       </c>
       <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -984,6 +999,7 @@
         <v>28</v>
       </c>
       <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1029,6 +1045,7 @@
         <v>49</v>
       </c>
       <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1074,6 +1091,7 @@
         <v>40</v>
       </c>
       <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1119,6 +1137,7 @@
         <v>29</v>
       </c>
       <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1164,6 +1183,7 @@
         <v>54</v>
       </c>
       <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1209,6 +1229,7 @@
         <v>41</v>
       </c>
       <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1254,6 +1275,7 @@
         <v>48</v>
       </c>
       <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1299,6 +1321,7 @@
         <v>48</v>
       </c>
       <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1344,6 +1367,7 @@
         <v>31</v>
       </c>
       <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1389,6 +1413,7 @@
         <v>47</v>
       </c>
       <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1434,6 +1459,7 @@
         <v>47</v>
       </c>
       <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1479,6 +1505,7 @@
         <v>49</v>
       </c>
       <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1524,6 +1551,7 @@
         <v>42</v>
       </c>
       <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1569,6 +1597,7 @@
         <v>56</v>
       </c>
       <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1614,6 +1643,7 @@
         <v>33</v>
       </c>
       <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1659,6 +1689,7 @@
         <v>29</v>
       </c>
       <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1704,6 +1735,7 @@
         <v>23</v>
       </c>
       <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1749,6 +1781,7 @@
         <v>48</v>
       </c>
       <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1794,6 +1827,7 @@
         <v>53</v>
       </c>
       <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1839,6 +1873,7 @@
         <v>26</v>
       </c>
       <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1884,6 +1919,7 @@
         <v>38</v>
       </c>
       <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1929,6 +1965,7 @@
         <v>29</v>
       </c>
       <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1974,6 +2011,7 @@
         <v>47</v>
       </c>
       <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2019,6 +2057,7 @@
         <v>51</v>
       </c>
       <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2064,6 +2103,7 @@
         <v>50</v>
       </c>
       <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2109,6 +2149,7 @@
         <v>36</v>
       </c>
       <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2154,6 +2195,7 @@
         <v>49</v>
       </c>
       <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2199,6 +2241,7 @@
         <v>23</v>
       </c>
       <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2244,6 +2287,7 @@
         <v>39</v>
       </c>
       <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2289,6 +2333,7 @@
         <v>41</v>
       </c>
       <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2334,6 +2379,7 @@
         <v>59</v>
       </c>
       <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2379,6 +2425,7 @@
         <v>48</v>
       </c>
       <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2424,6 +2471,7 @@
         <v>12</v>
       </c>
       <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2469,6 +2517,7 @@
         <v>26</v>
       </c>
       <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2514,6 +2563,7 @@
         <v>36</v>
       </c>
       <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2559,6 +2609,7 @@
         <v>23</v>
       </c>
       <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2604,6 +2655,7 @@
         <v>52</v>
       </c>
       <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2649,6 +2701,7 @@
         <v>48</v>
       </c>
       <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2694,6 +2747,7 @@
         <v>47</v>
       </c>
       <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2739,6 +2793,7 @@
         <v>50</v>
       </c>
       <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2784,6 +2839,7 @@
         <v>38</v>
       </c>
       <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2829,6 +2885,7 @@
         <v>25</v>
       </c>
       <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2874,6 +2931,7 @@
         <v>38</v>
       </c>
       <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2919,6 +2977,7 @@
         <v>32</v>
       </c>
       <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2964,6 +3023,7 @@
         <v>47</v>
       </c>
       <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3009,6 +3069,7 @@
         <v>34</v>
       </c>
       <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3054,6 +3115,7 @@
         <v>50</v>
       </c>
       <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3099,6 +3161,7 @@
         <v>29</v>
       </c>
       <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3144,6 +3207,7 @@
         <v>30</v>
       </c>
       <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3189,6 +3253,7 @@
         <v>6</v>
       </c>
       <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3234,6 +3299,7 @@
         <v>67</v>
       </c>
       <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3279,6 +3345,7 @@
         <v>47</v>
       </c>
       <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3324,6 +3391,7 @@
         <v>44</v>
       </c>
       <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3369,6 +3437,7 @@
         <v>69</v>
       </c>
       <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3414,6 +3483,7 @@
         <v>42</v>
       </c>
       <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3459,6 +3529,7 @@
         <v>59</v>
       </c>
       <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3504,6 +3575,7 @@
         <v>20</v>
       </c>
       <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3549,6 +3621,7 @@
         <v>48</v>
       </c>
       <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3594,6 +3667,7 @@
         <v>32</v>
       </c>
       <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3639,6 +3713,7 @@
         <v>42</v>
       </c>
       <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3684,6 +3759,7 @@
         <v>44</v>
       </c>
       <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3729,6 +3805,7 @@
         <v>65</v>
       </c>
       <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3774,6 +3851,7 @@
         <v>69</v>
       </c>
       <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3819,6 +3897,7 @@
         <v>29</v>
       </c>
       <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3864,6 +3943,7 @@
         <v>23</v>
       </c>
       <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3909,6 +3989,7 @@
         <v>43</v>
       </c>
       <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3954,6 +4035,7 @@
         <v>43</v>
       </c>
       <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3999,6 +4081,7 @@
         <v>40</v>
       </c>
       <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4044,6 +4127,7 @@
         <v>55</v>
       </c>
       <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4089,6 +4173,7 @@
         <v>51</v>
       </c>
       <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4134,6 +4219,7 @@
         <v>46</v>
       </c>
       <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4179,6 +4265,7 @@
         <v>46</v>
       </c>
       <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4224,6 +4311,7 @@
         <v>27</v>
       </c>
       <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4269,6 +4357,7 @@
         <v>27</v>
       </c>
       <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4314,6 +4403,7 @@
         <v>26</v>
       </c>
       <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4359,6 +4449,7 @@
         <v>52</v>
       </c>
       <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4404,6 +4495,7 @@
         <v>47</v>
       </c>
       <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4449,6 +4541,7 @@
         <v>42</v>
       </c>
       <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4494,6 +4587,7 @@
         <v>41</v>
       </c>
       <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4539,6 +4633,7 @@
         <v>34</v>
       </c>
       <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4584,6 +4679,7 @@
         <v>68</v>
       </c>
       <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4629,6 +4725,7 @@
         <v>24</v>
       </c>
       <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4674,6 +4771,7 @@
         <v>33</v>
       </c>
       <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4719,6 +4817,7 @@
         <v>29</v>
       </c>
       <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4764,6 +4863,7 @@
         <v>43</v>
       </c>
       <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4809,6 +4909,7 @@
         <v>49</v>
       </c>
       <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4854,6 +4955,7 @@
         <v>49</v>
       </c>
       <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4899,6 +5001,7 @@
         <v>42</v>
       </c>
       <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4944,6 +5047,7 @@
         <v>17</v>
       </c>
       <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4989,6 +5093,7 @@
         <v>40</v>
       </c>
       <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5034,6 +5139,7 @@
         <v>45</v>
       </c>
       <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5079,6 +5185,7 @@
         <v>21</v>
       </c>
       <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5124,6 +5231,7 @@
         <v>18</v>
       </c>
       <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5169,6 +5277,7 @@
         <v>58</v>
       </c>
       <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5214,6 +5323,7 @@
         <v>45</v>
       </c>
       <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5259,6 +5369,7 @@
         <v>50</v>
       </c>
       <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5304,6 +5415,7 @@
         <v>29</v>
       </c>
       <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5349,6 +5461,7 @@
         <v>24</v>
       </c>
       <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5394,6 +5507,7 @@
         <v>33</v>
       </c>
       <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5439,6 +5553,7 @@
         <v>30</v>
       </c>
       <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5484,6 +5599,7 @@
         <v>44</v>
       </c>
       <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5529,6 +5645,7 @@
         <v>50</v>
       </c>
       <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5574,6 +5691,7 @@
         <v>92</v>
       </c>
       <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5619,6 +5737,7 @@
         <v>29</v>
       </c>
       <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5664,6 +5783,7 @@
         <v>44</v>
       </c>
       <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5709,6 +5829,7 @@
         <v>31</v>
       </c>
       <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5754,6 +5875,7 @@
         <v>48</v>
       </c>
       <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5799,6 +5921,7 @@
         <v>3</v>
       </c>
       <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5844,6 +5967,7 @@
         <v>27</v>
       </c>
       <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5889,6 +6013,7 @@
         <v>40</v>
       </c>
       <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5934,6 +6059,7 @@
         <v>38</v>
       </c>
       <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5979,6 +6105,7 @@
         <v>47</v>
       </c>
       <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6024,6 +6151,7 @@
         <v>53</v>
       </c>
       <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6069,6 +6197,7 @@
         <v>40</v>
       </c>
       <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6114,6 +6243,7 @@
         <v>38</v>
       </c>
       <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6159,6 +6289,7 @@
         <v>37</v>
       </c>
       <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6204,6 +6335,7 @@
         <v>45</v>
       </c>
       <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6249,6 +6381,7 @@
         <v>47</v>
       </c>
       <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6294,6 +6427,7 @@
         <v>38</v>
       </c>
       <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6339,6 +6473,7 @@
         <v>19</v>
       </c>
       <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6384,6 +6519,7 @@
         <v>38</v>
       </c>
       <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6429,6 +6565,7 @@
         <v>45</v>
       </c>
       <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6474,6 +6611,7 @@
         <v>42</v>
       </c>
       <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6519,6 +6657,7 @@
         <v>49</v>
       </c>
       <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6564,6 +6703,7 @@
         <v>39</v>
       </c>
       <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6609,6 +6749,7 @@
         <v>20</v>
       </c>
       <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6654,6 +6795,7 @@
         <v>20</v>
       </c>
       <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6699,6 +6841,7 @@
         <v>58</v>
       </c>
       <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6744,6 +6887,7 @@
         <v>58</v>
       </c>
       <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6789,6 +6933,7 @@
         <v>57</v>
       </c>
       <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6834,6 +6979,7 @@
         <v>48</v>
       </c>
       <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6879,6 +7025,7 @@
         <v>25</v>
       </c>
       <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6924,6 +7071,7 @@
         <v>59</v>
       </c>
       <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6969,6 +7117,7 @@
         <v>47</v>
       </c>
       <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7014,6 +7163,7 @@
         <v>40</v>
       </c>
       <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7059,6 +7209,7 @@
         <v>48</v>
       </c>
       <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7104,6 +7255,7 @@
         <v>26</v>
       </c>
       <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7149,6 +7301,7 @@
         <v>70</v>
       </c>
       <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7194,6 +7347,7 @@
         <v>37</v>
       </c>
       <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7239,6 +7393,7 @@
         <v>42</v>
       </c>
       <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7284,6 +7439,7 @@
         <v>32</v>
       </c>
       <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7329,6 +7485,7 @@
         <v>58</v>
       </c>
       <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7374,6 +7531,7 @@
         <v>42</v>
       </c>
       <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7419,6 +7577,7 @@
         <v>34</v>
       </c>
       <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7464,6 +7623,7 @@
         <v>48</v>
       </c>
       <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7509,6 +7669,7 @@
         <v>50</v>
       </c>
       <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7554,6 +7715,7 @@
         <v>59</v>
       </c>
       <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7599,6 +7761,7 @@
         <v>62</v>
       </c>
       <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7644,6 +7807,7 @@
         <v>57</v>
       </c>
       <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7689,6 +7853,7 @@
         <v>42</v>
       </c>
       <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7734,6 +7899,7 @@
         <v>68</v>
       </c>
       <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7779,6 +7945,7 @@
         <v>52</v>
       </c>
       <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7824,6 +7991,7 @@
         <v>64</v>
       </c>
       <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7869,6 +8037,7 @@
         <v>65</v>
       </c>
       <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7914,6 +8083,7 @@
         <v>48</v>
       </c>
       <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7959,6 +8129,7 @@
         <v>30</v>
       </c>
       <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8004,6 +8175,7 @@
         <v>29</v>
       </c>
       <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8049,6 +8221,7 @@
         <v>51</v>
       </c>
       <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8094,6 +8267,7 @@
         <v>25</v>
       </c>
       <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8139,6 +8313,7 @@
         <v>32</v>
       </c>
       <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8184,6 +8359,7 @@
         <v>31</v>
       </c>
       <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8229,6 +8405,7 @@
         <v>51</v>
       </c>
       <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8274,6 +8451,7 @@
         <v>47</v>
       </c>
       <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8319,6 +8497,7 @@
         <v>18</v>
       </c>
       <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8364,6 +8543,7 @@
         <v>50</v>
       </c>
       <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8409,6 +8589,7 @@
         <v>16</v>
       </c>
       <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8454,6 +8635,7 @@
         <v>48</v>
       </c>
       <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8499,6 +8681,7 @@
         <v>54</v>
       </c>
       <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8544,6 +8727,7 @@
         <v>55</v>
       </c>
       <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8589,6 +8773,7 @@
         <v>49</v>
       </c>
       <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -8634,6 +8819,7 @@
         <v>57</v>
       </c>
       <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8679,6 +8865,7 @@
         <v>23</v>
       </c>
       <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8724,6 +8911,7 @@
         <v>45</v>
       </c>
       <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8769,6 +8957,7 @@
         <v>21</v>
       </c>
       <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8814,6 +9003,7 @@
         <v>57</v>
       </c>
       <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8859,6 +9049,7 @@
         <v>49</v>
       </c>
       <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8904,6 +9095,7 @@
         <v>53</v>
       </c>
       <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8949,6 +9141,7 @@
         <v>46</v>
       </c>
       <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8994,6 +9187,7 @@
         <v>64</v>
       </c>
       <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -9039,6 +9233,7 @@
         <v>58</v>
       </c>
       <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9084,6 +9279,7 @@
         <v>61</v>
       </c>
       <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9129,6 +9325,7 @@
         <v>60</v>
       </c>
       <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9174,6 +9371,7 @@
         <v>36</v>
       </c>
       <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9219,6 +9417,7 @@
         <v>26</v>
       </c>
       <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -9264,6 +9463,7 @@
         <v>32</v>
       </c>
       <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -9309,6 +9509,7 @@
         <v>63</v>
       </c>
       <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -9354,6 +9555,7 @@
         <v>59</v>
       </c>
       <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -9399,6 +9601,7 @@
         <v>40</v>
       </c>
       <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -9444,6 +9647,7 @@
         <v>31</v>
       </c>
       <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -9489,6 +9693,7 @@
         <v>-200</v>
       </c>
       <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -9534,6 +9739,7 @@
         <v>47</v>
       </c>
       <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -9579,6 +9785,7 @@
         <v>43</v>
       </c>
       <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -9624,6 +9831,7 @@
         <v>56</v>
       </c>
       <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -9669,6 +9877,7 @@
         <v>65</v>
       </c>
       <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -9714,6 +9923,7 @@
         <v>37</v>
       </c>
       <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -9759,6 +9969,7 @@
         <v>58</v>
       </c>
       <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -9804,6 +10015,7 @@
         <v>87</v>
       </c>
       <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -9849,6 +10061,7 @@
         <v>58</v>
       </c>
       <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -9894,6 +10107,7 @@
         <v>59</v>
       </c>
       <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -9939,6 +10153,7 @@
         <v>52</v>
       </c>
       <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -9984,6 +10199,7 @@
         <v>38</v>
       </c>
       <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -10029,6 +10245,7 @@
         <v>55</v>
       </c>
       <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -10074,6 +10291,7 @@
         <v>47</v>
       </c>
       <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -10119,6 +10337,7 @@
         <v>45</v>
       </c>
       <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -10164,6 +10383,7 @@
         <v>70</v>
       </c>
       <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -10209,6 +10429,7 @@
         <v>61</v>
       </c>
       <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -10254,6 +10475,7 @@
         <v>57</v>
       </c>
       <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -10299,6 +10521,7 @@
         <v>54</v>
       </c>
       <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -10344,6 +10567,7 @@
         <v>45</v>
       </c>
       <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -10389,6 +10613,7 @@
         <v>28</v>
       </c>
       <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -10434,6 +10659,7 @@
         <v>55</v>
       </c>
       <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -10479,6 +10705,7 @@
         <v>79</v>
       </c>
       <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -10524,6 +10751,7 @@
         <v>69</v>
       </c>
       <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -10566,6 +10794,7 @@
         <v>0</v>
       </c>
       <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -10611,6 +10840,7 @@
         <v>38</v>
       </c>
       <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -10656,6 +10886,7 @@
         <v>54</v>
       </c>
       <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -10701,6 +10932,7 @@
         <v>38</v>
       </c>
       <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -10746,6 +10978,7 @@
         <v>40</v>
       </c>
       <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -10791,6 +11024,7 @@
         <v>57</v>
       </c>
       <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -10836,6 +11070,7 @@
         <v>59</v>
       </c>
       <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -10881,6 +11116,7 @@
         <v>67</v>
       </c>
       <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -10926,6 +11162,7 @@
         <v>51</v>
       </c>
       <c r="N233" t="inlineStr"/>
+      <c r="O233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -10971,6 +11208,7 @@
         <v>64</v>
       </c>
       <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -11016,6 +11254,7 @@
         <v>60</v>
       </c>
       <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -11061,6 +11300,7 @@
         <v>60</v>
       </c>
       <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -11106,6 +11346,7 @@
         <v>39</v>
       </c>
       <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -11151,6 +11392,7 @@
         <v>50</v>
       </c>
       <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -11196,6 +11438,7 @@
         <v>47</v>
       </c>
       <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -11241,6 +11484,7 @@
         <v>65</v>
       </c>
       <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -11286,6 +11530,7 @@
         <v>42</v>
       </c>
       <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -11331,6 +11576,7 @@
         <v>49</v>
       </c>
       <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -11376,6 +11622,7 @@
         <v>81</v>
       </c>
       <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -11421,6 +11668,7 @@
         <v>47</v>
       </c>
       <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -11466,6 +11714,7 @@
         <v>51</v>
       </c>
       <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -11511,6 +11760,7 @@
         <v>64</v>
       </c>
       <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -11553,6 +11803,7 @@
         <v>51</v>
       </c>
       <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -11595,6 +11846,7 @@
         <v>-80</v>
       </c>
       <c r="N248" t="inlineStr"/>
+      <c r="O248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -11637,6 +11889,7 @@
         <v>46</v>
       </c>
       <c r="N249" t="inlineStr"/>
+      <c r="O249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -11679,6 +11932,7 @@
         <v>49</v>
       </c>
       <c r="N250" t="inlineStr"/>
+      <c r="O250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -11721,6 +11975,7 @@
         <v>3</v>
       </c>
       <c r="N251" t="inlineStr"/>
+      <c r="O251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -11763,6 +12018,7 @@
         <v>7</v>
       </c>
       <c r="N252" t="inlineStr"/>
+      <c r="O252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -11805,6 +12061,7 @@
         <v>50</v>
       </c>
       <c r="N253" t="inlineStr"/>
+      <c r="O253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -11847,6 +12104,7 @@
         <v>59</v>
       </c>
       <c r="N254" t="inlineStr"/>
+      <c r="O254" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Other Recommended Order.xlsx
+++ b/data/Other Recommended Order.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Being Removed" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Transfer Plan" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O253"/>
+  <dimension ref="A1:P253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +495,11 @@
           <t>Buy Month</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -540,6 +546,7 @@
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -586,6 +593,7 @@
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -632,6 +640,7 @@
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -678,6 +687,7 @@
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -724,6 +734,7 @@
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -770,6 +781,7 @@
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -816,6 +828,7 @@
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -862,6 +875,7 @@
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -908,6 +922,7 @@
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -954,6 +969,7 @@
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1000,6 +1016,7 @@
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1046,6 +1063,7 @@
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1092,6 +1110,7 @@
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1138,6 +1157,7 @@
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1184,6 +1204,7 @@
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1230,6 +1251,7 @@
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1276,6 +1298,7 @@
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1322,6 +1345,7 @@
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1368,6 +1392,7 @@
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1414,6 +1439,7 @@
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1460,6 +1486,7 @@
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1506,6 +1533,7 @@
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1552,6 +1580,7 @@
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1598,6 +1627,7 @@
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1644,6 +1674,7 @@
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1690,6 +1721,7 @@
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1736,6 +1768,7 @@
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1782,6 +1815,7 @@
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1828,6 +1862,7 @@
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1874,6 +1909,7 @@
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1920,6 +1956,7 @@
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1966,6 +2003,7 @@
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2012,6 +2050,7 @@
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2058,6 +2097,7 @@
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2104,6 +2144,7 @@
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2150,6 +2191,7 @@
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2196,6 +2238,7 @@
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2242,6 +2285,7 @@
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2288,6 +2332,7 @@
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2334,6 +2379,7 @@
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2380,6 +2426,7 @@
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2426,6 +2473,7 @@
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2472,6 +2520,7 @@
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2518,6 +2567,7 @@
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2564,6 +2614,7 @@
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2610,6 +2661,7 @@
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2656,6 +2708,7 @@
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2702,6 +2755,7 @@
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2748,6 +2802,7 @@
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2794,6 +2849,7 @@
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2840,6 +2896,7 @@
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2886,6 +2943,7 @@
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2932,6 +2990,7 @@
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2978,6 +3037,7 @@
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3024,6 +3084,7 @@
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3070,6 +3131,7 @@
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3116,6 +3178,7 @@
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3162,6 +3225,7 @@
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3208,6 +3272,7 @@
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3254,6 +3319,7 @@
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3300,6 +3366,7 @@
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3346,6 +3413,7 @@
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3392,6 +3460,7 @@
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3438,6 +3507,7 @@
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3484,6 +3554,7 @@
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3530,6 +3601,7 @@
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3576,6 +3648,7 @@
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3622,6 +3695,7 @@
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3668,6 +3742,7 @@
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3714,6 +3789,7 @@
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3760,6 +3836,7 @@
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3806,6 +3883,7 @@
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3852,6 +3930,7 @@
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3898,6 +3977,7 @@
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3944,6 +4024,7 @@
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3990,6 +4071,7 @@
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4036,6 +4118,7 @@
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4082,6 +4165,7 @@
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4128,6 +4212,7 @@
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4174,6 +4259,7 @@
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4220,6 +4306,7 @@
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4266,6 +4353,7 @@
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4312,6 +4400,7 @@
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4358,6 +4447,7 @@
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4404,6 +4494,7 @@
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4450,6 +4541,7 @@
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4496,6 +4588,7 @@
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4542,6 +4635,7 @@
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4588,6 +4682,7 @@
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4634,6 +4729,7 @@
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4680,6 +4776,7 @@
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4726,6 +4823,7 @@
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4772,6 +4870,7 @@
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4818,6 +4917,7 @@
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4864,6 +4964,7 @@
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4910,6 +5011,7 @@
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4956,6 +5058,7 @@
       </c>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5002,6 +5105,7 @@
       </c>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5048,6 +5152,7 @@
       </c>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5094,6 +5199,7 @@
       </c>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5140,6 +5246,7 @@
       </c>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5186,6 +5293,7 @@
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5232,6 +5340,7 @@
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5278,6 +5387,7 @@
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5324,6 +5434,7 @@
       </c>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5370,6 +5481,7 @@
       </c>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5416,6 +5528,7 @@
       </c>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5462,6 +5575,7 @@
       </c>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5508,6 +5622,7 @@
       </c>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5554,6 +5669,7 @@
       </c>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5600,6 +5716,7 @@
       </c>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5646,6 +5763,7 @@
       </c>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5692,6 +5810,7 @@
       </c>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5738,6 +5857,7 @@
       </c>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5784,6 +5904,7 @@
       </c>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5830,6 +5951,7 @@
       </c>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5876,6 +5998,7 @@
       </c>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5922,6 +6045,7 @@
       </c>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5968,6 +6092,7 @@
       </c>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6014,6 +6139,7 @@
       </c>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6060,6 +6186,7 @@
       </c>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6106,6 +6233,7 @@
       </c>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6152,6 +6280,7 @@
       </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6198,6 +6327,7 @@
       </c>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6244,6 +6374,7 @@
       </c>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6290,6 +6421,7 @@
       </c>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6336,6 +6468,7 @@
       </c>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6382,6 +6515,7 @@
       </c>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6428,6 +6562,7 @@
       </c>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6474,6 +6609,7 @@
       </c>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6520,6 +6656,7 @@
       </c>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6566,6 +6703,7 @@
       </c>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6612,6 +6750,7 @@
       </c>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6658,6 +6797,7 @@
       </c>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6704,6 +6844,7 @@
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6750,6 +6891,7 @@
       </c>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6796,6 +6938,7 @@
       </c>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6842,6 +6985,7 @@
       </c>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6888,6 +7032,7 @@
       </c>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6934,6 +7079,7 @@
       </c>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6980,6 +7126,7 @@
       </c>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7026,6 +7173,7 @@
       </c>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7072,6 +7220,7 @@
       </c>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7118,6 +7267,7 @@
       </c>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7164,6 +7314,7 @@
       </c>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7210,6 +7361,7 @@
       </c>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7256,6 +7408,7 @@
       </c>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7302,6 +7455,7 @@
       </c>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7348,6 +7502,7 @@
       </c>
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7394,6 +7549,7 @@
       </c>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7440,6 +7596,7 @@
       </c>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7486,6 +7643,7 @@
       </c>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7532,6 +7690,7 @@
       </c>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7578,6 +7737,7 @@
       </c>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7624,6 +7784,7 @@
       </c>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7670,6 +7831,7 @@
       </c>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7716,6 +7878,7 @@
       </c>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7762,6 +7925,7 @@
       </c>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7808,6 +7972,7 @@
       </c>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7854,6 +8019,7 @@
       </c>
       <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7900,6 +8066,7 @@
       </c>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7946,6 +8113,7 @@
       </c>
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7992,6 +8160,7 @@
       </c>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8038,6 +8207,7 @@
       </c>
       <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8084,6 +8254,7 @@
       </c>
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8130,6 +8301,7 @@
       </c>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8176,6 +8348,7 @@
       </c>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8222,6 +8395,7 @@
       </c>
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8268,6 +8442,7 @@
       </c>
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8314,6 +8489,7 @@
       </c>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8360,6 +8536,7 @@
       </c>
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8406,6 +8583,7 @@
       </c>
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8452,6 +8630,7 @@
       </c>
       <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8498,6 +8677,7 @@
       </c>
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8544,6 +8724,7 @@
       </c>
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8590,6 +8771,7 @@
       </c>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8636,6 +8818,7 @@
       </c>
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8682,6 +8865,7 @@
       </c>
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8728,6 +8912,7 @@
       </c>
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8774,6 +8959,7 @@
       </c>
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -8820,6 +9006,7 @@
       </c>
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8866,6 +9053,7 @@
       </c>
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8912,6 +9100,7 @@
       </c>
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8958,6 +9147,7 @@
       </c>
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9004,6 +9194,7 @@
       </c>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
+      <c r="P186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9050,6 +9241,7 @@
       </c>
       <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9096,6 +9288,7 @@
       </c>
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9142,6 +9335,7 @@
       </c>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9188,6 +9382,7 @@
       </c>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -9234,6 +9429,7 @@
       </c>
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9280,6 +9476,7 @@
       </c>
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9326,6 +9523,7 @@
       </c>
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9372,6 +9570,7 @@
       </c>
       <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9418,6 +9617,7 @@
       </c>
       <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -9464,6 +9664,7 @@
       </c>
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -9510,6 +9711,7 @@
       </c>
       <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -9556,6 +9758,7 @@
       </c>
       <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -9602,6 +9805,7 @@
       </c>
       <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -9648,6 +9852,11 @@
       </c>
       <c r="N200" t="inlineStr"/>
       <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Margin looks off - check retail/cost</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -9694,6 +9903,7 @@
       </c>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -9740,6 +9950,7 @@
       </c>
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -9786,6 +9997,7 @@
       </c>
       <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -9832,6 +10044,7 @@
       </c>
       <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -9878,6 +10091,7 @@
       </c>
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -9924,6 +10138,7 @@
       </c>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -9970,6 +10185,7 @@
       </c>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10016,6 +10232,7 @@
       </c>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -10062,6 +10279,7 @@
       </c>
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -10108,6 +10326,7 @@
       </c>
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -10154,6 +10373,7 @@
       </c>
       <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -10200,6 +10420,7 @@
       </c>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -10246,6 +10467,7 @@
       </c>
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -10292,6 +10514,7 @@
       </c>
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -10338,6 +10561,7 @@
       </c>
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr"/>
+      <c r="P215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -10384,6 +10608,7 @@
       </c>
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr"/>
+      <c r="P216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -10430,6 +10655,7 @@
       </c>
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -10476,6 +10702,7 @@
       </c>
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
+      <c r="P218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -10522,6 +10749,7 @@
       </c>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
+      <c r="P219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -10568,6 +10796,7 @@
       </c>
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr"/>
+      <c r="P220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -10614,6 +10843,7 @@
       </c>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
+      <c r="P221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -10660,6 +10890,7 @@
       </c>
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -10706,6 +10937,7 @@
       </c>
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -10752,6 +10984,7 @@
       </c>
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -10795,6 +11028,11 @@
       </c>
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>No cost data - verify price; Margin looks off - check retail/cost</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -10841,6 +11079,7 @@
       </c>
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -10887,6 +11126,7 @@
       </c>
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr"/>
+      <c r="P227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -10933,6 +11173,7 @@
       </c>
       <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr"/>
+      <c r="P228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -10979,6 +11220,7 @@
       </c>
       <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -11025,6 +11267,7 @@
       </c>
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr"/>
+      <c r="P230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -11071,6 +11314,7 @@
       </c>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr"/>
+      <c r="P231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -11117,6 +11361,7 @@
       </c>
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -11163,6 +11408,7 @@
       </c>
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -11209,6 +11455,7 @@
       </c>
       <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -11255,6 +11502,7 @@
       </c>
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -11301,6 +11549,7 @@
       </c>
       <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr"/>
+      <c r="P236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -11347,6 +11596,7 @@
       </c>
       <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr"/>
+      <c r="P237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -11393,6 +11643,7 @@
       </c>
       <c r="N238" t="inlineStr"/>
       <c r="O238" t="inlineStr"/>
+      <c r="P238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -11439,6 +11690,7 @@
       </c>
       <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr"/>
+      <c r="P239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -11485,6 +11737,7 @@
       </c>
       <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr"/>
+      <c r="P240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -11531,6 +11784,7 @@
       </c>
       <c r="N241" t="inlineStr"/>
       <c r="O241" t="inlineStr"/>
+      <c r="P241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -11577,6 +11831,7 @@
       </c>
       <c r="N242" t="inlineStr"/>
       <c r="O242" t="inlineStr"/>
+      <c r="P242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -11623,6 +11878,7 @@
       </c>
       <c r="N243" t="inlineStr"/>
       <c r="O243" t="inlineStr"/>
+      <c r="P243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -11669,6 +11925,7 @@
       </c>
       <c r="N244" t="inlineStr"/>
       <c r="O244" t="inlineStr"/>
+      <c r="P244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -11715,6 +11972,7 @@
       </c>
       <c r="N245" t="inlineStr"/>
       <c r="O245" t="inlineStr"/>
+      <c r="P245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -11758,6 +12016,7 @@
       </c>
       <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr"/>
+      <c r="P246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -11801,6 +12060,11 @@
       </c>
       <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr"/>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>Margin looks off - check retail/cost</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -11844,6 +12108,7 @@
       </c>
       <c r="N248" t="inlineStr"/>
       <c r="O248" t="inlineStr"/>
+      <c r="P248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -11887,6 +12152,7 @@
       </c>
       <c r="N249" t="inlineStr"/>
       <c r="O249" t="inlineStr"/>
+      <c r="P249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -11930,6 +12196,7 @@
       </c>
       <c r="N250" t="inlineStr"/>
       <c r="O250" t="inlineStr"/>
+      <c r="P250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -11973,6 +12240,7 @@
       </c>
       <c r="N251" t="inlineStr"/>
       <c r="O251" t="inlineStr"/>
+      <c r="P251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -12016,6 +12284,7 @@
       </c>
       <c r="N252" t="inlineStr"/>
       <c r="O252" t="inlineStr"/>
+      <c r="P252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -12059,6 +12328,7 @@
       </c>
       <c r="N253" t="inlineStr"/>
       <c r="O253" t="inlineStr"/>
+      <c r="P253" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12071,7 +12341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12145,16 +12415,26 @@
           <t>Deal Terms</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Buy Month</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Coco Lopez Cream of Coconut 15oz</t>
+          <t>Spooky Sriracha 32oz</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Condiments</t>
+          <t>Mixes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -12163,83 +12443,92 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>113</v>
+        <v>177</v>
       </c>
       <c r="E2" t="n">
-        <v>15.1</v>
+        <v>56.1</v>
       </c>
       <c r="F2" t="n">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="G2" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>24.01</v>
       </c>
       <c r="K2" t="n">
-        <v>60</v>
+        <v>576</v>
       </c>
       <c r="L2" t="n">
-        <v>17</v>
+        <v>-200</v>
       </c>
       <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Margin looks off - check retail/cost</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Codigo Organic Agave Nectar 12oz</t>
+          <t>Top Ten Branded Wine Tote Bags</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Condiments</t>
+          <t>Wine Tote</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E3" t="n">
-        <v>27.4</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J3" t="n">
-        <v>5.72</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>69</v>
-      </c>
-      <c r="L3" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>No cost data - verify price; Margin looks off - check retail/cost</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dashfire Mole Bitters 50ml</t>
+          <t>7up 20oz</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -12249,667 +12538,40 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Am Craft Spirits</t>
+          <t>American Bottling Company</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E4" t="n">
-        <v>64.3</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>9.52</v>
+        <v>3.59</v>
       </c>
       <c r="K4" t="n">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="L4" t="n">
-        <v>46</v>
+        <v>-80</v>
       </c>
       <c r="N4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Fever Tree Bloody Mary Mix 750ml</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Mixes</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Dahlheimer Beverage Monticello</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>62</v>
-      </c>
-      <c r="E5" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="K5" t="n">
-        <v>35</v>
-      </c>
-      <c r="L5" t="n">
-        <v>42</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Fever Tree Classic Margarita Mix 750ml</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Mixes</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>68</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="F6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>12</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="K6" t="n">
-        <v>60</v>
-      </c>
-      <c r="L6" t="n">
-        <v>50</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Fever Tree Club Soda 8pk 5oz can</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Mixes</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>92</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>15</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>15</v>
-      </c>
-      <c r="I7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K7" t="n">
-        <v>83</v>
-      </c>
-      <c r="L7" t="n">
-        <v>45</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Fever Tree Elderflower Tonic 4pk 6.7oz btl</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Mixes</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>102</v>
-      </c>
-      <c r="E8" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F8" t="n">
-        <v>20</v>
-      </c>
-      <c r="G8" t="n">
-        <v>16</v>
-      </c>
-      <c r="H8" t="n">
-        <v>6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="K8" t="n">
-        <v>21</v>
-      </c>
-      <c r="L8" t="n">
-        <v>46</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Fever Tree Ginger Ale 4pk 6.7oz btl</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Mixes</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>83</v>
-      </c>
-      <c r="E9" t="n">
-        <v>15</v>
-      </c>
-      <c r="F9" t="n">
-        <v>49</v>
-      </c>
-      <c r="G9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K9" t="n">
-        <v>23</v>
-      </c>
-      <c r="L9" t="n">
-        <v>40</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fever Tree Light Margarita Mix 750ml</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Mixes</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>46</v>
-      </c>
-      <c r="E10" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="F10" t="n">
-        <v>29</v>
-      </c>
-      <c r="G10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" t="n">
-        <v>24</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="K10" t="n">
-        <v>109</v>
-      </c>
-      <c r="L10" t="n">
-        <v>54</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Fever Tree Light Tonic Water 4pk 6.7oz btl</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Mixes</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>71</v>
-      </c>
-      <c r="E11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F11" t="n">
-        <v>29</v>
-      </c>
-      <c r="G11" t="n">
-        <v>24</v>
-      </c>
-      <c r="H11" t="n">
-        <v>6</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="K11" t="n">
-        <v>19</v>
-      </c>
-      <c r="L11" t="n">
-        <v>50</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fever Tree Light Tonic Water 8pk 5oz can</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Mixes</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>66</v>
-      </c>
-      <c r="E12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="K12" t="n">
-        <v>16</v>
-      </c>
-      <c r="L12" t="n">
-        <v>48</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Fever Tree Sparkling Lime &amp; Yuzu 4pk 6.7oz btl</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Mixes</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Dahlheimer Beverage Monticello</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>75</v>
-      </c>
-      <c r="E13" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="F13" t="n">
-        <v>60</v>
-      </c>
-      <c r="G13" t="n">
-        <v>33</v>
-      </c>
-      <c r="H13" t="n">
-        <v>24</v>
-      </c>
-      <c r="I13" t="n">
-        <v>4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K13" t="n">
-        <v>87</v>
-      </c>
-      <c r="L13" t="n">
-        <v>44</v>
-      </c>
-      <c r="N13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fever Tree Sparkling Sicilian Lemonade 4pk 6.7oz btl</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Mixes</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>114</v>
-      </c>
-      <c r="E14" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F14" t="n">
-        <v>96</v>
-      </c>
-      <c r="G14" t="n">
-        <v>85</v>
-      </c>
-      <c r="H14" t="n">
-        <v>12</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="K14" t="n">
-        <v>45</v>
-      </c>
-      <c r="L14" t="n">
-        <v>42</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fever Tree Tonic Water 8pk 5oz can</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Mixes</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>79</v>
-      </c>
-      <c r="E15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="F15" t="n">
-        <v>11</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" t="n">
-        <v>4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="K15" t="n">
-        <v>66</v>
-      </c>
-      <c r="L15" t="n">
-        <v>45</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Lovejoy's Thai Basil Bloody Mary Mix 25oz</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Mixes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Johnson Brothers - St. Paul</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>101</v>
-      </c>
-      <c r="E16" t="n">
-        <v>135.3</v>
-      </c>
-      <c r="F16" t="n">
-        <v>12</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>12</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>10.47</v>
-      </c>
-      <c r="K16" t="n">
-        <v>126</v>
-      </c>
-      <c r="L16" t="n">
-        <v>35</v>
-      </c>
-      <c r="N16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Roses Sweetened Lime Juice 25oz</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Mixes</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Bellboy Corporation</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>104</v>
-      </c>
-      <c r="E17" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F17" t="n">
-        <v>30</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>24</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="K17" t="n">
-        <v>142</v>
-      </c>
-      <c r="L17" t="n">
-        <v>15</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Zing Zang Michelada 32oz</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Mixes</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>44</v>
-      </c>
-      <c r="E18" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="F18" t="n">
-        <v>12</v>
-      </c>
-      <c r="G18" t="n">
-        <v>5</v>
-      </c>
-      <c r="H18" t="n">
-        <v>6</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="K18" t="n">
-        <v>22</v>
-      </c>
-      <c r="L18" t="n">
-        <v>47</v>
-      </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Margin looks off - check retail/cost</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12922,6 +12584,857 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Chain OH (TOH)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>WOS</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Gross Need</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Buy Units</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Buy Cases</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Net Buy $</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>GM %</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Discount %</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Deal Terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Coco Lopez Cream of Coconut 15oz</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Condiments</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Bellboy Corporation</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>113</v>
+      </c>
+      <c r="E2" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G2" t="n">
+        <v>57</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>60</v>
+      </c>
+      <c r="L2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Codigo Organic Agave Nectar 12oz</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Condiments</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>178</v>
+      </c>
+      <c r="E3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>81</v>
+      </c>
+      <c r="G3" t="n">
+        <v>72</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="K3" t="n">
+        <v>69</v>
+      </c>
+      <c r="L3" t="n">
+        <v>36</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dashfire Mole Bitters 50ml</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Mixes</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Am Craft Spirits</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="K4" t="n">
+        <v>57</v>
+      </c>
+      <c r="L4" t="n">
+        <v>46</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Fever Tree Bloody Mary Mix 750ml</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Mixes</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Dahlheimer Beverage Monticello</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>62</v>
+      </c>
+      <c r="E5" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="K5" t="n">
+        <v>35</v>
+      </c>
+      <c r="L5" t="n">
+        <v>42</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fever Tree Classic Margarita Mix 750ml</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mixes</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>68</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="K6" t="n">
+        <v>60</v>
+      </c>
+      <c r="L6" t="n">
+        <v>50</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Fever Tree Club Soda 8pk 5oz can</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mixes</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>92</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>15</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>83</v>
+      </c>
+      <c r="L7" t="n">
+        <v>45</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Fever Tree Elderflower Tonic 4pk 6.7oz btl</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mixes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>102</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="K8" t="n">
+        <v>21</v>
+      </c>
+      <c r="L8" t="n">
+        <v>46</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Fever Tree Ginger Ale 4pk 6.7oz btl</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mixes</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>83</v>
+      </c>
+      <c r="E9" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" t="n">
+        <v>49</v>
+      </c>
+      <c r="G9" t="n">
+        <v>45</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K9" t="n">
+        <v>23</v>
+      </c>
+      <c r="L9" t="n">
+        <v>40</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fever Tree Light Margarita Mix 750ml</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mixes</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>46</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>29</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="K10" t="n">
+        <v>109</v>
+      </c>
+      <c r="L10" t="n">
+        <v>54</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Fever Tree Light Tonic Water 4pk 6.7oz btl</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mixes</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>71</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>29</v>
+      </c>
+      <c r="G11" t="n">
+        <v>24</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="K11" t="n">
+        <v>19</v>
+      </c>
+      <c r="L11" t="n">
+        <v>50</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fever Tree Light Tonic Water 8pk 5oz can</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mixes</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>66</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="K12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L12" t="n">
+        <v>48</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fever Tree Sparkling Lime &amp; Yuzu 4pk 6.7oz btl</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mixes</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Dahlheimer Beverage Monticello</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>75</v>
+      </c>
+      <c r="E13" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>60</v>
+      </c>
+      <c r="G13" t="n">
+        <v>33</v>
+      </c>
+      <c r="H13" t="n">
+        <v>24</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87</v>
+      </c>
+      <c r="L13" t="n">
+        <v>44</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fever Tree Sparkling Sicilian Lemonade 4pk 6.7oz btl</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mixes</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>114</v>
+      </c>
+      <c r="E14" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>96</v>
+      </c>
+      <c r="G14" t="n">
+        <v>85</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="K14" t="n">
+        <v>45</v>
+      </c>
+      <c r="L14" t="n">
+        <v>42</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fever Tree Tonic Water 8pk 5oz can</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mixes</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>79</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="K15" t="n">
+        <v>66</v>
+      </c>
+      <c r="L15" t="n">
+        <v>45</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Lovejoy's Thai Basil Bloody Mary Mix 25oz</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mixes</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>101</v>
+      </c>
+      <c r="E16" t="n">
+        <v>135.3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>12</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="K16" t="n">
+        <v>126</v>
+      </c>
+      <c r="L16" t="n">
+        <v>35</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Roses Sweetened Lime Juice 25oz</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Mixes</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Bellboy Corporation</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>104</v>
+      </c>
+      <c r="E17" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>30</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>24</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="K17" t="n">
+        <v>142</v>
+      </c>
+      <c r="L17" t="n">
+        <v>15</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Zing Zang Michelada 32oz</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Mixes</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>44</v>
+      </c>
+      <c r="E18" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F18" t="n">
+        <v>12</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>6</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="K18" t="n">
+        <v>22</v>
+      </c>
+      <c r="L18" t="n">
+        <v>47</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I807"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/data/Other Recommended Order.xlsx
+++ b/data/Other Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Other Recommended Order.xlsx
+++ b/data/Other Recommended Order.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Transfer Plan" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Other Recommended Order.xlsx
+++ b/data/Other Recommended Order.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Transfer Plan" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Other Recommended Order.xlsx
+++ b/data/Other Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q87"/>
+  <dimension ref="A1:S87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,55 +452,65 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>LY wk</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Gross Need</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Buy Units</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Buy Cases</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Net Buy $</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>GM %</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Discount %</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Deal Terms</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Buy Month</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
@@ -524,26 +534,32 @@
         <v>-28.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1734</v>
+        <v>177</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>20.2</v>
       </c>
       <c r="I2" t="n">
         <v>1734</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>1734</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+        <v>1734</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>No cost data - verify price; Margin looks off - check retail/cost</t>
         </is>
@@ -567,7 +583,7 @@
         <v>-4.3</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -576,17 +592,23 @@
         <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
       </c>
       <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
         <v>4</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
         <is>
           <t>Margin looks off - check retail/cost</t>
         </is>
@@ -620,29 +642,35 @@
         <v>-2.9</v>
       </c>
       <c r="G4" t="n">
+        <v>78</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>26</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>24</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>3</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>2.45</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>59</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>39</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -672,7 +700,7 @@
         <v>-2.6</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>-52</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -681,20 +709,26 @@
         <v>8</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>1.95</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>16</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>51</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -724,29 +758,35 @@
         <v>-1.4</v>
       </c>
       <c r="G6" t="n">
+        <v>149</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>91</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>100</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>4</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>1.48</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>148</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>17</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -776,29 +816,35 @@
         <v>-1.1</v>
       </c>
       <c r="G7" t="n">
+        <v>33</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I7" t="n">
         <v>5</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>6</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>4.59</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>28</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>23</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -828,7 +874,7 @@
         <v>-0.8</v>
       </c>
       <c r="G8" t="n">
-        <v>24</v>
+        <v>-11</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -837,20 +883,26 @@
         <v>24</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>24</v>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.92</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>22</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>74</v>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -880,29 +932,35 @@
         <v>-0.2</v>
       </c>
       <c r="G9" t="n">
+        <v>90</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I9" t="n">
         <v>19</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>24</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>2</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>3.67</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>88</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>39</v>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -922,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>140</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -931,20 +989,26 @@
         <v>4</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>4</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>100</v>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
         <is>
           <t>No cost data - verify price; Margin over 95% - check retail</t>
         </is>
@@ -968,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -977,20 +1041,26 @@
         <v>1</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>100</v>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
         <is>
           <t>No cost data - verify price; Margin over 95% - check retail</t>
         </is>
@@ -1024,29 +1094,35 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
+        <v>-43</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>24</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>25</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>5</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>8.41</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>210</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>30</v>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1071,7 +1147,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1080,20 +1156,26 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
         <v>74.67</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>75</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>49</v>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1123,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1132,20 +1214,26 @@
         <v>15</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>15</v>
+      </c>
+      <c r="L14" t="n">
         <v>3</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>8.41</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>126</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>27</v>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1170,7 +1258,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1179,20 +1267,26 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>22</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
+        <v>22</v>
+      </c>
+      <c r="M15" t="n">
         <v>2.42</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>53</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>46</v>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1222,29 +1316,35 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I16" t="n">
         <v>24</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>24</v>
+      </c>
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>3.1</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>74</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>31</v>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1274,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1283,20 +1383,26 @@
         <v>1</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
         <v>11.3</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>11</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>75</v>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1326,29 +1432,35 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
+        <v>140</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>7</v>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>5</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>8.41</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>42</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>30</v>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1378,29 +1490,35 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
+        <v>110</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>7</v>
       </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>5</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>8.41</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>42</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>27</v>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1430,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1439,20 +1557,26 @@
         <v>5</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>8.41</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>42</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>27</v>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1472,7 +1596,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1481,20 +1605,26 @@
         <v>105</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>105</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>100</v>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
         <is>
           <t>No cost data - verify price; Margin over 95% - check retail</t>
         </is>
@@ -1523,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1532,20 +1662,26 @@
         <v>4</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>4</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>100</v>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
         <is>
           <t>No cost data - verify price; Margin over 95% - check retail</t>
         </is>
@@ -1579,29 +1715,35 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>2</v>
       </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>3</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>4.37</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>13</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>33</v>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1626,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>-59</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1635,20 +1777,26 @@
         <v>4</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>4</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
+        <v>4</v>
+      </c>
+      <c r="M24" t="n">
         <v>1.41</v>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
         <v>6</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>32</v>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1678,29 +1826,35 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
+        <v>33</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>4</v>
       </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>5</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>8</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>40</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>-0</v>
       </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1730,29 +1884,35 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
+        <v>91</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
         <v>7</v>
       </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>5</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>8</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>40</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>-0</v>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1772,26 +1932,32 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>222</v>
+        <v>-4</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I27" t="n">
         <v>222</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>222</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
       <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
+        <v>222</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
         <is>
           <t>No cost data - verify price; Margin looks off - check retail/cost</t>
         </is>
@@ -1820,29 +1986,35 @@
         <v>0.1</v>
       </c>
       <c r="G28" t="n">
+        <v>65</v>
+      </c>
+      <c r="H28" t="n">
+        <v>446</v>
+      </c>
+      <c r="I28" t="n">
         <v>2212</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>21</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>2191</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>2191</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>3.28</v>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
         <v>7189</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>49</v>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
         <is>
           <t>Large buy ($7,189) - confirm</t>
         </is>
@@ -1876,29 +2048,35 @@
         <v>0.1</v>
       </c>
       <c r="G29" t="n">
+        <v>-27</v>
+      </c>
+      <c r="H29" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="I29" t="n">
         <v>26</v>
       </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>25</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>5</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>8.41</v>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
         <v>210</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>16</v>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1928,29 +2106,35 @@
         <v>0.3</v>
       </c>
       <c r="G30" t="n">
+        <v>200</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>13</v>
       </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>15</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.88</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>13</v>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>62</v>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1980,29 +2164,35 @@
         <v>0.6</v>
       </c>
       <c r="G31" t="n">
-        <v>35</v>
+        <v>-17</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I31" t="n">
         <v>35</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>35</v>
+      </c>
+      <c r="L31" t="n">
         <v>7</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>8.41</v>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
         <v>294</v>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>24</v>
       </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2032,7 +2222,7 @@
         <v>0.6</v>
       </c>
       <c r="G32" t="n">
-        <v>6</v>
+        <v>162</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2041,20 +2231,26 @@
         <v>6</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
         <v>6</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
+        <v>6</v>
+      </c>
+      <c r="M32" t="n">
         <v>94</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>564</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>15</v>
       </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2079,7 +2275,7 @@
         <v>0.6</v>
       </c>
       <c r="G33" t="n">
-        <v>18</v>
+        <v>-7</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -2088,20 +2284,26 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>18</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
+        <v>18</v>
+      </c>
+      <c r="M33" t="n">
         <v>1.23</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>22</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>65</v>
       </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2131,29 +2333,35 @@
         <v>0.8</v>
       </c>
       <c r="G34" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
         <v>23</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
         <v>23</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
+        <v>23</v>
+      </c>
+      <c r="M34" t="n">
         <v>5.03</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
         <v>116</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>56</v>
       </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2183,29 +2391,35 @@
         <v>0.8</v>
       </c>
       <c r="G35" t="n">
+        <v>30</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
         <v>66</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>10</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>60</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>5</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>1.84</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>111</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>47</v>
       </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2235,29 +2449,35 @@
         <v>0.8</v>
       </c>
       <c r="G36" t="n">
+        <v>85</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I36" t="n">
         <v>16</v>
       </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
         <v>18</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>2.93</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>53</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>47</v>
       </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2287,29 +2507,35 @@
         <v>0.8</v>
       </c>
       <c r="G37" t="n">
+        <v>65</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
         <v>17</v>
       </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
         <v>12</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>1.79</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>21</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>49</v>
       </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2339,29 +2565,35 @@
         <v>0.9</v>
       </c>
       <c r="G38" t="n">
+        <v>9</v>
+      </c>
+      <c r="H38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I38" t="n">
         <v>78</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>22</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>60</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>5</v>
       </c>
-      <c r="K38" t="n">
+      <c r="M38" t="n">
         <v>1.82</v>
       </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
         <v>109</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>48</v>
       </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2391,29 +2623,35 @@
         <v>0.9</v>
       </c>
       <c r="G39" t="n">
+        <v>200</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
         <v>4</v>
       </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>6</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>4.67</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>28</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>48</v>
       </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2443,29 +2681,35 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
+        <v>108</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
         <v>6</v>
       </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>5</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>1</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>8.41</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>42</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>27</v>
       </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2495,29 +2739,35 @@
         <v>1.1</v>
       </c>
       <c r="G41" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>16.2</v>
       </c>
       <c r="I41" t="n">
         <v>48</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>48</v>
+      </c>
+      <c r="L41" t="n">
         <v>12</v>
       </c>
-      <c r="K41" t="n">
+      <c r="M41" t="n">
         <v>4.36</v>
       </c>
-      <c r="L41" t="n">
+      <c r="N41" t="n">
         <v>209</v>
       </c>
-      <c r="M41" t="n">
+      <c r="O41" t="n">
         <v>52</v>
       </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2547,29 +2797,35 @@
         <v>1.1</v>
       </c>
       <c r="G42" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
         <v>10</v>
       </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>12</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>1</v>
       </c>
-      <c r="K42" t="n">
+      <c r="M42" t="n">
         <v>1.79</v>
       </c>
-      <c r="L42" t="n">
+      <c r="N42" t="n">
         <v>21</v>
       </c>
-      <c r="M42" t="n">
+      <c r="O42" t="n">
         <v>49</v>
       </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2599,29 +2855,35 @@
         <v>1.2</v>
       </c>
       <c r="G43" t="n">
+        <v>63</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>22</v>
       </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>24</v>
       </c>
-      <c r="J43" t="n">
+      <c r="L43" t="n">
         <v>2</v>
       </c>
-      <c r="K43" t="n">
+      <c r="M43" t="n">
         <v>1.73</v>
       </c>
-      <c r="L43" t="n">
+      <c r="N43" t="n">
         <v>42</v>
       </c>
-      <c r="M43" t="n">
+      <c r="O43" t="n">
         <v>42</v>
       </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2651,7 +2913,7 @@
         <v>1.3</v>
       </c>
       <c r="G44" t="n">
-        <v>20</v>
+        <v>-38</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2660,20 +2922,26 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>20</v>
+      </c>
+      <c r="L44" t="n">
         <v>4</v>
       </c>
-      <c r="K44" t="n">
+      <c r="M44" t="n">
         <v>8.41</v>
       </c>
-      <c r="L44" t="n">
+      <c r="N44" t="n">
         <v>168</v>
       </c>
-      <c r="M44" t="n">
+      <c r="O44" t="n">
         <v>30</v>
       </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2703,29 +2971,35 @@
         <v>1.3</v>
       </c>
       <c r="G45" t="n">
+        <v>-44</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
         <v>11</v>
       </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" t="n">
+      <c r="L45" t="n">
         <v>2</v>
       </c>
-      <c r="K45" t="n">
+      <c r="M45" t="n">
         <v>8.41</v>
       </c>
-      <c r="L45" t="n">
+      <c r="N45" t="n">
         <v>84</v>
       </c>
-      <c r="M45" t="n">
+      <c r="O45" t="n">
         <v>27</v>
       </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2755,29 +3029,35 @@
         <v>1.3</v>
       </c>
       <c r="G46" t="n">
-        <v>15</v>
+        <v>-48</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="I46" t="n">
         <v>15</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>15</v>
+      </c>
+      <c r="L46" t="n">
         <v>3</v>
       </c>
-      <c r="K46" t="n">
+      <c r="M46" t="n">
         <v>8.41</v>
       </c>
-      <c r="L46" t="n">
+      <c r="N46" t="n">
         <v>126</v>
       </c>
-      <c r="M46" t="n">
+      <c r="O46" t="n">
         <v>16</v>
       </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2807,29 +3087,35 @@
         <v>1.4</v>
       </c>
       <c r="G47" t="n">
+        <v>-43</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
         <v>13</v>
       </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
         <v>15</v>
       </c>
-      <c r="J47" t="n">
+      <c r="L47" t="n">
         <v>3</v>
       </c>
-      <c r="K47" t="n">
+      <c r="M47" t="n">
         <v>8.41</v>
       </c>
-      <c r="L47" t="n">
+      <c r="N47" t="n">
         <v>126</v>
       </c>
-      <c r="M47" t="n">
+      <c r="O47" t="n">
         <v>30</v>
       </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2859,29 +3145,35 @@
         <v>1.5</v>
       </c>
       <c r="G48" t="n">
+        <v>44</v>
+      </c>
+      <c r="H48" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I48" t="n">
         <v>14</v>
       </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>12</v>
       </c>
-      <c r="J48" t="n">
+      <c r="L48" t="n">
         <v>2</v>
       </c>
-      <c r="K48" t="n">
+      <c r="M48" t="n">
         <v>2.19</v>
       </c>
-      <c r="L48" t="n">
+      <c r="N48" t="n">
         <v>26</v>
       </c>
-      <c r="M48" t="n">
+      <c r="O48" t="n">
         <v>60</v>
       </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2911,29 +3203,35 @@
         <v>1.6</v>
       </c>
       <c r="G49" t="n">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I49" t="n">
         <v>24</v>
       </c>
       <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>24</v>
+      </c>
+      <c r="L49" t="n">
         <v>4</v>
       </c>
-      <c r="K49" t="n">
+      <c r="M49" t="n">
         <v>3.67</v>
       </c>
-      <c r="L49" t="n">
+      <c r="N49" t="n">
         <v>88</v>
       </c>
-      <c r="M49" t="n">
+      <c r="O49" t="n">
         <v>47</v>
       </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2963,29 +3261,35 @@
         <v>1.6</v>
       </c>
       <c r="G50" t="n">
+        <v>56</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
         <v>7</v>
       </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
         <v>5</v>
       </c>
-      <c r="J50" t="n">
+      <c r="L50" t="n">
         <v>1</v>
       </c>
-      <c r="K50" t="n">
+      <c r="M50" t="n">
         <v>8.41</v>
       </c>
-      <c r="L50" t="n">
+      <c r="N50" t="n">
         <v>42</v>
       </c>
-      <c r="M50" t="n">
+      <c r="O50" t="n">
         <v>27</v>
       </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3010,29 +3314,35 @@
         <v>1.7</v>
       </c>
       <c r="G51" t="n">
+        <v>42</v>
+      </c>
+      <c r="H51" t="n">
+        <v>665</v>
+      </c>
+      <c r="I51" t="n">
         <v>1993</v>
       </c>
-      <c r="H51" t="n">
+      <c r="J51" t="n">
         <v>275</v>
       </c>
-      <c r="I51" t="n">
+      <c r="K51" t="n">
         <v>1718</v>
       </c>
-      <c r="J51" t="n">
+      <c r="L51" t="n">
         <v>1718</v>
       </c>
-      <c r="K51" t="n">
+      <c r="M51" t="n">
         <v>1.25</v>
       </c>
-      <c r="L51" t="n">
+      <c r="N51" t="n">
         <v>2147</v>
       </c>
-      <c r="M51" t="n">
+      <c r="O51" t="n">
         <v>64</v>
       </c>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3057,29 +3367,35 @@
         <v>1.8</v>
       </c>
       <c r="G52" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I52" t="n">
         <v>41</v>
       </c>
       <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
         <v>41</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
+        <v>41</v>
+      </c>
+      <c r="M52" t="n">
         <v>5.64</v>
       </c>
-      <c r="L52" t="n">
+      <c r="N52" t="n">
         <v>231</v>
       </c>
-      <c r="M52" t="n">
+      <c r="O52" t="n">
         <v>51</v>
       </c>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3109,29 +3425,35 @@
         <v>1.8</v>
       </c>
       <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I53" t="n">
         <v>19</v>
       </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
         <v>24</v>
       </c>
-      <c r="J53" t="n">
+      <c r="L53" t="n">
         <v>2</v>
       </c>
-      <c r="K53" t="n">
+      <c r="M53" t="n">
         <v>1.5</v>
       </c>
-      <c r="L53" t="n">
+      <c r="N53" t="n">
         <v>36</v>
       </c>
-      <c r="M53" t="n">
+      <c r="O53" t="n">
         <v>57</v>
       </c>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3161,29 +3483,35 @@
         <v>1.9</v>
       </c>
       <c r="G54" t="n">
-        <v>28</v>
+        <v>-9</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="I54" t="n">
         <v>28</v>
       </c>
       <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>28</v>
+      </c>
+      <c r="L54" t="n">
         <v>7</v>
       </c>
-      <c r="K54" t="n">
+      <c r="M54" t="n">
         <v>4.53</v>
       </c>
-      <c r="L54" t="n">
+      <c r="N54" t="n">
         <v>127</v>
       </c>
-      <c r="M54" t="n">
+      <c r="O54" t="n">
         <v>50</v>
       </c>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3216,26 +3544,32 @@
         <v>26</v>
       </c>
       <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>26</v>
+      </c>
+      <c r="J55" t="n">
         <v>12</v>
       </c>
-      <c r="I55" t="n">
+      <c r="K55" t="n">
         <v>15</v>
       </c>
-      <c r="J55" t="n">
+      <c r="L55" t="n">
         <v>3</v>
       </c>
-      <c r="K55" t="n">
+      <c r="M55" t="n">
         <v>8.41</v>
       </c>
-      <c r="L55" t="n">
+      <c r="N55" t="n">
         <v>126</v>
       </c>
-      <c r="M55" t="n">
+      <c r="O55" t="n">
         <v>30</v>
       </c>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3265,29 +3599,35 @@
         <v>2.1</v>
       </c>
       <c r="G56" t="n">
+        <v>100</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
         <v>17</v>
       </c>
-      <c r="H56" t="n">
+      <c r="J56" t="n">
         <v>8</v>
       </c>
-      <c r="I56" t="n">
+      <c r="K56" t="n">
         <v>12</v>
       </c>
-      <c r="J56" t="n">
+      <c r="L56" t="n">
         <v>1</v>
       </c>
-      <c r="K56" t="n">
+      <c r="M56" t="n">
         <v>1.79</v>
       </c>
-      <c r="L56" t="n">
+      <c r="N56" t="n">
         <v>21</v>
       </c>
-      <c r="M56" t="n">
+      <c r="O56" t="n">
         <v>49</v>
       </c>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3312,7 +3652,7 @@
         <v>2.1</v>
       </c>
       <c r="G57" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -3321,20 +3661,26 @@
         <v>6</v>
       </c>
       <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
         <v>6</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
+        <v>6</v>
+      </c>
+      <c r="M57" t="n">
         <v>3.21</v>
       </c>
-      <c r="L57" t="n">
+      <c r="N57" t="n">
         <v>19</v>
       </c>
-      <c r="M57" t="n">
+      <c r="O57" t="n">
         <v>7</v>
       </c>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3364,29 +3710,35 @@
         <v>2.2</v>
       </c>
       <c r="G58" t="n">
+        <v>63</v>
+      </c>
+      <c r="H58" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I58" t="n">
         <v>32</v>
       </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
         <v>30</v>
       </c>
-      <c r="J58" t="n">
+      <c r="L58" t="n">
         <v>6</v>
       </c>
-      <c r="K58" t="n">
+      <c r="M58" t="n">
         <v>8.41</v>
       </c>
-      <c r="L58" t="n">
+      <c r="N58" t="n">
         <v>252</v>
       </c>
-      <c r="M58" t="n">
+      <c r="O58" t="n">
         <v>27</v>
       </c>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3416,7 +3768,7 @@
         <v>2.3</v>
       </c>
       <c r="G59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -3425,20 +3777,26 @@
         <v>15</v>
       </c>
       <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>15</v>
+      </c>
+      <c r="L59" t="n">
         <v>3</v>
       </c>
-      <c r="K59" t="n">
+      <c r="M59" t="n">
         <v>8.41</v>
       </c>
-      <c r="L59" t="n">
+      <c r="N59" t="n">
         <v>126</v>
       </c>
-      <c r="M59" t="n">
+      <c r="O59" t="n">
         <v>30</v>
       </c>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3468,29 +3826,35 @@
         <v>2.5</v>
       </c>
       <c r="G60" t="n">
+        <v>18</v>
+      </c>
+      <c r="H60" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="I60" t="n">
         <v>105</v>
       </c>
-      <c r="H60" t="n">
+      <c r="J60" t="n">
         <v>39</v>
       </c>
-      <c r="I60" t="n">
+      <c r="K60" t="n">
         <v>72</v>
       </c>
-      <c r="J60" t="n">
+      <c r="L60" t="n">
         <v>6</v>
       </c>
-      <c r="K60" t="n">
+      <c r="M60" t="n">
         <v>5.87</v>
       </c>
-      <c r="L60" t="n">
+      <c r="N60" t="n">
         <v>422</v>
       </c>
-      <c r="M60" t="n">
+      <c r="O60" t="n">
         <v>49</v>
       </c>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3520,29 +3884,35 @@
         <v>2.5</v>
       </c>
       <c r="G61" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H61" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I61" t="n">
         <v>43</v>
       </c>
-      <c r="H61" t="n">
+      <c r="J61" t="n">
         <v>10</v>
       </c>
-      <c r="I61" t="n">
+      <c r="K61" t="n">
         <v>36</v>
       </c>
-      <c r="J61" t="n">
+      <c r="L61" t="n">
         <v>6</v>
       </c>
-      <c r="K61" t="n">
+      <c r="M61" t="n">
         <v>3.73</v>
       </c>
-      <c r="L61" t="n">
+      <c r="N61" t="n">
         <v>134</v>
       </c>
-      <c r="M61" t="n">
+      <c r="O61" t="n">
         <v>32</v>
       </c>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3572,29 +3942,35 @@
         <v>2.6</v>
       </c>
       <c r="G62" t="n">
+        <v>105</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I62" t="n">
         <v>14</v>
       </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
         <v>12</v>
       </c>
-      <c r="J62" t="n">
+      <c r="L62" t="n">
         <v>1</v>
       </c>
-      <c r="K62" t="n">
+      <c r="M62" t="n">
         <v>4.35</v>
       </c>
-      <c r="L62" t="n">
+      <c r="N62" t="n">
         <v>52</v>
       </c>
-      <c r="M62" t="n">
+      <c r="O62" t="n">
         <v>46</v>
       </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3619,7 +3995,7 @@
         <v>2.6</v>
       </c>
       <c r="G63" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3628,20 +4004,26 @@
         <v>7</v>
       </c>
       <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
         <v>7</v>
       </c>
-      <c r="K63" t="n">
+      <c r="L63" t="n">
+        <v>7</v>
+      </c>
+      <c r="M63" t="n">
         <v>2.06</v>
       </c>
-      <c r="L63" t="n">
+      <c r="N63" t="n">
         <v>14</v>
       </c>
-      <c r="M63" t="n">
+      <c r="O63" t="n">
         <v>17</v>
       </c>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3671,29 +4053,35 @@
         <v>2.7</v>
       </c>
       <c r="G64" t="n">
+        <v>14</v>
+      </c>
+      <c r="H64" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I64" t="n">
         <v>118</v>
       </c>
-      <c r="H64" t="n">
+      <c r="J64" t="n">
         <v>33</v>
       </c>
-      <c r="I64" t="n">
+      <c r="K64" t="n">
         <v>96</v>
       </c>
-      <c r="J64" t="n">
+      <c r="L64" t="n">
         <v>4</v>
       </c>
-      <c r="K64" t="n">
+      <c r="M64" t="n">
         <v>0.99</v>
       </c>
-      <c r="L64" t="n">
+      <c r="N64" t="n">
         <v>95</v>
       </c>
-      <c r="M64" t="n">
+      <c r="O64" t="n">
         <v>57</v>
       </c>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3723,29 +4111,35 @@
         <v>2.7</v>
       </c>
       <c r="G65" t="n">
+        <v>5</v>
+      </c>
+      <c r="H65" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="I65" t="n">
         <v>121</v>
       </c>
-      <c r="H65" t="n">
+      <c r="J65" t="n">
         <v>37</v>
       </c>
-      <c r="I65" t="n">
+      <c r="K65" t="n">
         <v>80</v>
       </c>
-      <c r="J65" t="n">
+      <c r="L65" t="n">
         <v>10</v>
       </c>
-      <c r="K65" t="n">
+      <c r="M65" t="n">
         <v>3.21</v>
       </c>
-      <c r="L65" t="n">
+      <c r="N65" t="n">
         <v>257</v>
       </c>
-      <c r="M65" t="n">
+      <c r="O65" t="n">
         <v>29</v>
       </c>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3775,29 +4169,35 @@
         <v>2.7</v>
       </c>
       <c r="G66" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H66" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I66" t="n">
         <v>6</v>
       </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
         <v>8</v>
       </c>
-      <c r="J66" t="n">
+      <c r="L66" t="n">
         <v>2</v>
       </c>
-      <c r="K66" t="n">
+      <c r="M66" t="n">
         <v>6</v>
       </c>
-      <c r="L66" t="n">
+      <c r="N66" t="n">
         <v>48</v>
       </c>
-      <c r="M66" t="n">
+      <c r="O66" t="n">
         <v>40</v>
       </c>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3822,29 +4222,35 @@
         <v>2.8</v>
       </c>
       <c r="G67" t="n">
+        <v>32</v>
+      </c>
+      <c r="H67" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="I67" t="n">
         <v>56</v>
       </c>
-      <c r="H67" t="n">
+      <c r="J67" t="n">
         <v>25</v>
       </c>
-      <c r="I67" t="n">
+      <c r="K67" t="n">
         <v>31</v>
       </c>
-      <c r="J67" t="n">
+      <c r="L67" t="n">
         <v>31</v>
       </c>
-      <c r="K67" t="n">
+      <c r="M67" t="n">
         <v>5.49</v>
       </c>
-      <c r="L67" t="n">
+      <c r="N67" t="n">
         <v>170</v>
       </c>
-      <c r="M67" t="n">
+      <c r="O67" t="n">
         <v>50</v>
       </c>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3874,29 +4280,35 @@
         <v>2.9</v>
       </c>
       <c r="G68" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H68" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="I68" t="n">
         <v>84</v>
       </c>
-      <c r="H68" t="n">
+      <c r="J68" t="n">
         <v>33</v>
       </c>
-      <c r="I68" t="n">
+      <c r="K68" t="n">
         <v>48</v>
       </c>
-      <c r="J68" t="n">
+      <c r="L68" t="n">
         <v>6</v>
       </c>
-      <c r="K68" t="n">
+      <c r="M68" t="n">
         <v>3.21</v>
       </c>
-      <c r="L68" t="n">
+      <c r="N68" t="n">
         <v>154</v>
       </c>
-      <c r="M68" t="n">
+      <c r="O68" t="n">
         <v>29</v>
       </c>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3926,29 +4338,35 @@
         <v>2.9</v>
       </c>
       <c r="G69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H69" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="I69" t="n">
         <v>64</v>
       </c>
-      <c r="H69" t="n">
+      <c r="J69" t="n">
         <v>37</v>
       </c>
-      <c r="I69" t="n">
+      <c r="K69" t="n">
         <v>24</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>2</v>
       </c>
-      <c r="K69" t="n">
+      <c r="M69" t="n">
         <v>1.84</v>
       </c>
-      <c r="L69" t="n">
+      <c r="N69" t="n">
         <v>44</v>
       </c>
-      <c r="M69" t="n">
+      <c r="O69" t="n">
         <v>47</v>
       </c>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3978,29 +4396,35 @@
         <v>2.9</v>
       </c>
       <c r="G70" t="n">
+        <v>3</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I70" t="n">
         <v>27</v>
       </c>
-      <c r="H70" t="n">
+      <c r="J70" t="n">
         <v>15</v>
       </c>
-      <c r="I70" t="n">
+      <c r="K70" t="n">
         <v>12</v>
       </c>
-      <c r="J70" t="n">
+      <c r="L70" t="n">
         <v>1</v>
       </c>
-      <c r="K70" t="n">
+      <c r="M70" t="n">
         <v>2.92</v>
       </c>
-      <c r="L70" t="n">
+      <c r="N70" t="n">
         <v>35</v>
       </c>
-      <c r="M70" t="n">
+      <c r="O70" t="n">
         <v>47</v>
       </c>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4030,29 +4454,35 @@
         <v>2.9</v>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I71" t="n">
         <v>2</v>
       </c>
       <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
         <v>2</v>
       </c>
-      <c r="K71" t="n">
+      <c r="L71" t="n">
+        <v>2</v>
+      </c>
+      <c r="M71" t="n">
         <v>59</v>
       </c>
-      <c r="L71" t="n">
+      <c r="N71" t="n">
         <v>118</v>
       </c>
-      <c r="M71" t="n">
+      <c r="O71" t="n">
         <v>16</v>
       </c>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4082,29 +4512,35 @@
         <v>2.9</v>
       </c>
       <c r="G72" t="n">
+        <v>80</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
         <v>2</v>
       </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
         <v>3</v>
       </c>
-      <c r="J72" t="n">
+      <c r="L72" t="n">
         <v>1</v>
       </c>
-      <c r="K72" t="n">
+      <c r="M72" t="n">
         <v>4.17</v>
       </c>
-      <c r="L72" t="n">
+      <c r="N72" t="n">
         <v>12</v>
       </c>
-      <c r="M72" t="n">
+      <c r="O72" t="n">
         <v>30</v>
       </c>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4134,29 +4570,35 @@
         <v>3</v>
       </c>
       <c r="G73" t="n">
+        <v>8</v>
+      </c>
+      <c r="H73" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="I73" t="n">
         <v>82</v>
       </c>
-      <c r="H73" t="n">
+      <c r="J73" t="n">
         <v>25</v>
       </c>
-      <c r="I73" t="n">
+      <c r="K73" t="n">
         <v>56</v>
       </c>
-      <c r="J73" t="n">
+      <c r="L73" t="n">
         <v>7</v>
       </c>
-      <c r="K73" t="n">
+      <c r="M73" t="n">
         <v>3.21</v>
       </c>
-      <c r="L73" t="n">
+      <c r="N73" t="n">
         <v>180</v>
       </c>
-      <c r="M73" t="n">
+      <c r="O73" t="n">
         <v>29</v>
       </c>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4186,29 +4628,35 @@
         <v>3</v>
       </c>
       <c r="G74" t="n">
+        <v>50</v>
+      </c>
+      <c r="H74" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I74" t="n">
         <v>8</v>
       </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
         <v>9</v>
       </c>
-      <c r="J74" t="n">
+      <c r="L74" t="n">
         <v>3</v>
       </c>
-      <c r="K74" t="n">
+      <c r="M74" t="n">
         <v>5.13</v>
       </c>
-      <c r="L74" t="n">
+      <c r="N74" t="n">
         <v>46</v>
       </c>
-      <c r="M74" t="n">
+      <c r="O74" t="n">
         <v>36</v>
       </c>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4238,29 +4686,35 @@
         <v>3.2</v>
       </c>
       <c r="G75" t="n">
+        <v>13</v>
+      </c>
+      <c r="H75" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="I75" t="n">
         <v>183</v>
       </c>
-      <c r="H75" t="n">
+      <c r="J75" t="n">
         <v>115</v>
       </c>
-      <c r="I75" t="n">
+      <c r="K75" t="n">
         <v>72</v>
       </c>
-      <c r="J75" t="n">
+      <c r="L75" t="n">
         <v>6</v>
       </c>
-      <c r="K75" t="n">
+      <c r="M75" t="n">
         <v>0.86</v>
       </c>
-      <c r="L75" t="n">
+      <c r="N75" t="n">
         <v>62</v>
       </c>
-      <c r="M75" t="n">
+      <c r="O75" t="n">
         <v>62</v>
       </c>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4290,29 +4744,35 @@
         <v>3.2</v>
       </c>
       <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="I76" t="n">
         <v>64</v>
       </c>
-      <c r="H76" t="n">
+      <c r="J76" t="n">
         <v>25</v>
       </c>
-      <c r="I76" t="n">
+      <c r="K76" t="n">
         <v>36</v>
       </c>
-      <c r="J76" t="n">
+      <c r="L76" t="n">
         <v>3</v>
       </c>
-      <c r="K76" t="n">
+      <c r="M76" t="n">
         <v>2.67</v>
       </c>
-      <c r="L76" t="n">
+      <c r="N76" t="n">
         <v>96</v>
       </c>
-      <c r="M76" t="n">
+      <c r="O76" t="n">
         <v>41</v>
       </c>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4342,29 +4802,35 @@
         <v>3.2</v>
       </c>
       <c r="G77" t="n">
+        <v>-16</v>
+      </c>
+      <c r="H77" t="n">
+        <v>7</v>
+      </c>
+      <c r="I77" t="n">
         <v>27</v>
       </c>
-      <c r="H77" t="n">
+      <c r="J77" t="n">
         <v>10</v>
       </c>
-      <c r="I77" t="n">
+      <c r="K77" t="n">
         <v>18</v>
       </c>
-      <c r="J77" t="n">
+      <c r="L77" t="n">
         <v>3</v>
       </c>
-      <c r="K77" t="n">
+      <c r="M77" t="n">
         <v>5.1</v>
       </c>
-      <c r="L77" t="n">
+      <c r="N77" t="n">
         <v>92</v>
       </c>
-      <c r="M77" t="n">
+      <c r="O77" t="n">
         <v>49</v>
       </c>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4394,29 +4860,35 @@
         <v>3.2</v>
       </c>
       <c r="G78" t="n">
+        <v>60</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
         <v>7</v>
       </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" t="n">
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
         <v>12</v>
       </c>
-      <c r="J78" t="n">
+      <c r="L78" t="n">
         <v>1</v>
       </c>
-      <c r="K78" t="n">
+      <c r="M78" t="n">
         <v>1.91</v>
       </c>
-      <c r="L78" t="n">
+      <c r="N78" t="n">
         <v>23</v>
       </c>
-      <c r="M78" t="n">
+      <c r="O78" t="n">
         <v>36</v>
       </c>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4441,29 +4913,35 @@
         <v>3.2</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I79" t="n">
         <v>1</v>
       </c>
       <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
         <v>1</v>
       </c>
-      <c r="K79" t="n">
+      <c r="L79" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" t="n">
         <v>4.17</v>
       </c>
-      <c r="L79" t="n">
+      <c r="N79" t="n">
         <v>4</v>
       </c>
-      <c r="M79" t="n">
+      <c r="O79" t="n">
         <v>16</v>
       </c>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4493,29 +4971,35 @@
         <v>3.3</v>
       </c>
       <c r="G80" t="n">
+        <v>25</v>
+      </c>
+      <c r="H80" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I80" t="n">
         <v>19</v>
       </c>
-      <c r="H80" t="n">
+      <c r="J80" t="n">
         <v>5</v>
       </c>
-      <c r="I80" t="n">
+      <c r="K80" t="n">
         <v>12</v>
       </c>
-      <c r="J80" t="n">
+      <c r="L80" t="n">
         <v>2</v>
       </c>
-      <c r="K80" t="n">
+      <c r="M80" t="n">
         <v>7.5</v>
       </c>
-      <c r="L80" t="n">
+      <c r="N80" t="n">
         <v>90</v>
       </c>
-      <c r="M80" t="n">
+      <c r="O80" t="n">
         <v>25</v>
       </c>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4540,7 +5024,7 @@
         <v>3.4</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -4549,20 +5033,26 @@
         <v>1</v>
       </c>
       <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
         <v>1</v>
       </c>
-      <c r="K81" t="n">
+      <c r="L81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" t="n">
         <v>2.09</v>
       </c>
-      <c r="L81" t="n">
+      <c r="N81" t="n">
         <v>2</v>
       </c>
-      <c r="M81" t="n">
+      <c r="O81" t="n">
         <v>40</v>
       </c>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4592,29 +5082,35 @@
         <v>3.5</v>
       </c>
       <c r="G82" t="n">
+        <v>6</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
         <v>14</v>
       </c>
-      <c r="H82" t="n">
+      <c r="J82" t="n">
         <v>10</v>
       </c>
-      <c r="I82" t="n">
+      <c r="K82" t="n">
         <v>4</v>
       </c>
-      <c r="J82" t="n">
+      <c r="L82" t="n">
         <v>2</v>
       </c>
-      <c r="K82" t="n">
+      <c r="M82" t="n">
         <v>9.65</v>
       </c>
-      <c r="L82" t="n">
+      <c r="N82" t="n">
         <v>39</v>
       </c>
-      <c r="M82" t="n">
+      <c r="O82" t="n">
         <v>23</v>
       </c>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4644,29 +5140,35 @@
         <v>3.6</v>
       </c>
       <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="I83" t="n">
         <v>54</v>
       </c>
-      <c r="H83" t="n">
+      <c r="J83" t="n">
         <v>35</v>
       </c>
-      <c r="I83" t="n">
+      <c r="K83" t="n">
         <v>16</v>
       </c>
-      <c r="J83" t="n">
+      <c r="L83" t="n">
         <v>2</v>
       </c>
-      <c r="K83" t="n">
+      <c r="M83" t="n">
         <v>3.21</v>
       </c>
-      <c r="L83" t="n">
+      <c r="N83" t="n">
         <v>51</v>
       </c>
-      <c r="M83" t="n">
+      <c r="O83" t="n">
         <v>29</v>
       </c>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4696,29 +5198,35 @@
         <v>3.7</v>
       </c>
       <c r="G84" t="n">
+        <v>25</v>
+      </c>
+      <c r="H84" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="I84" t="n">
         <v>46</v>
       </c>
-      <c r="H84" t="n">
+      <c r="J84" t="n">
         <v>30</v>
       </c>
-      <c r="I84" t="n">
+      <c r="K84" t="n">
         <v>12</v>
       </c>
-      <c r="J84" t="n">
+      <c r="L84" t="n">
         <v>1</v>
       </c>
-      <c r="K84" t="n">
+      <c r="M84" t="n">
         <v>4.37</v>
       </c>
-      <c r="L84" t="n">
+      <c r="N84" t="n">
         <v>52</v>
       </c>
-      <c r="M84" t="n">
+      <c r="O84" t="n">
         <v>12</v>
       </c>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4748,29 +5256,35 @@
         <v>3.8</v>
       </c>
       <c r="G85" t="n">
+        <v>22</v>
+      </c>
+      <c r="H85" t="n">
+        <v>17</v>
+      </c>
+      <c r="I85" t="n">
         <v>43</v>
       </c>
-      <c r="H85" t="n">
+      <c r="J85" t="n">
         <v>30</v>
       </c>
-      <c r="I85" t="n">
+      <c r="K85" t="n">
         <v>12</v>
       </c>
-      <c r="J85" t="n">
+      <c r="L85" t="n">
         <v>2</v>
       </c>
-      <c r="K85" t="n">
+      <c r="M85" t="n">
         <v>5.18</v>
       </c>
-      <c r="L85" t="n">
+      <c r="N85" t="n">
         <v>62</v>
       </c>
-      <c r="M85" t="n">
+      <c r="O85" t="n">
         <v>57</v>
       </c>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4800,7 +5314,7 @@
         <v>3.8</v>
       </c>
       <c r="G86" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -4809,20 +5323,26 @@
         <v>2</v>
       </c>
       <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>2</v>
+      </c>
+      <c r="L86" t="n">
         <v>1</v>
       </c>
-      <c r="K86" t="n">
+      <c r="M86" t="n">
         <v>9.65</v>
       </c>
-      <c r="L86" t="n">
+      <c r="N86" t="n">
         <v>19</v>
       </c>
-      <c r="M86" t="n">
+      <c r="O86" t="n">
         <v>23</v>
       </c>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4852,29 +5372,35 @@
         <v>3.9</v>
       </c>
       <c r="G87" t="n">
+        <v>11</v>
+      </c>
+      <c r="H87" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="I87" t="n">
         <v>49</v>
       </c>
-      <c r="H87" t="n">
+      <c r="J87" t="n">
         <v>34</v>
       </c>
-      <c r="I87" t="n">
+      <c r="K87" t="n">
         <v>12</v>
       </c>
-      <c r="J87" t="n">
+      <c r="L87" t="n">
         <v>1</v>
       </c>
-      <c r="K87" t="n">
+      <c r="M87" t="n">
         <v>3.52</v>
       </c>
-      <c r="L87" t="n">
+      <c r="N87" t="n">
         <v>42</v>
       </c>
-      <c r="M87" t="n">
+      <c r="O87" t="n">
         <v>22</v>
       </c>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4887,7 +5413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4923,55 +5449,65 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>LY wk</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Gross Need</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Buy Units</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Buy Cases</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Net Buy $</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>GM %</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Discount %</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Deal Terms</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Buy Month</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
@@ -4995,26 +5531,32 @@
         <v>-28.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1734</v>
+        <v>177</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>20.2</v>
       </c>
       <c r="I2" t="n">
         <v>1734</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>1734</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+        <v>1734</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>No cost data - verify price; Margin looks off - check retail/cost</t>
         </is>
@@ -5038,7 +5580,7 @@
         <v>-4.3</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -5047,17 +5589,23 @@
         <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
       </c>
       <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
         <v>4</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
         <is>
           <t>Margin looks off - check retail/cost</t>
         </is>
@@ -5081,7 +5629,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>140</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -5090,20 +5638,26 @@
         <v>4</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>4</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>100</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
         <is>
           <t>No cost data - verify price; Margin over 95% - check retail</t>
         </is>
@@ -5127,7 +5681,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -5136,20 +5690,26 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>100</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
         <is>
           <t>No cost data - verify price; Margin over 95% - check retail</t>
         </is>
@@ -5173,7 +5733,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -5182,20 +5742,26 @@
         <v>105</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>105</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>100</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
         <is>
           <t>No cost data - verify price; Margin over 95% - check retail</t>
         </is>
@@ -5224,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -5233,20 +5799,26 @@
         <v>4</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>4</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
         <v>100</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
         <is>
           <t>No cost data - verify price; Margin over 95% - check retail</t>
         </is>
@@ -5270,26 +5842,32 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>222</v>
+        <v>-4</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I8" t="n">
         <v>222</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>222</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+        <v>222</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
         <is>
           <t>No cost data - verify price; Margin looks off - check retail/cost</t>
         </is>
@@ -5318,29 +5896,35 @@
         <v>0.1</v>
       </c>
       <c r="G9" t="n">
+        <v>65</v>
+      </c>
+      <c r="H9" t="n">
+        <v>446</v>
+      </c>
+      <c r="I9" t="n">
         <v>2212</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>21</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>2191</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>2191</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>3.28</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>7189</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>49</v>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
         <is>
           <t>Large buy ($7,189) - confirm</t>
         </is>
@@ -5357,7 +5941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5393,45 +5977,55 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>LY wk</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Gross Need</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Buy Units</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Buy Cases</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Net Buy $</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>GM %</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Discount %</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Deal Terms</t>
         </is>
@@ -5465,27 +6059,33 @@
         <v>3.9</v>
       </c>
       <c r="G2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="I2" t="n">
         <v>45</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>32</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>12</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>4</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>5.58</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>67</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>44</v>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Other Recommended Order.xlsx
+++ b/data/Other Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
